--- a/research/traditional_assets/database/data/italy/italy_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_financial_svcs_non_bank_insurance.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06150000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="E2">
-        <v>0.09714999999999999</v>
+        <v>-0.033</v>
       </c>
       <c r="F2">
-        <v>0.09984999999999999</v>
+        <v>0.193</v>
       </c>
       <c r="G2">
-        <v>0.09192179395981961</v>
+        <v>0.06704599251698948</v>
       </c>
       <c r="H2">
-        <v>0.08998805223865135</v>
+        <v>0.06699076077273537</v>
       </c>
       <c r="I2">
-        <v>0.07769497986836744</v>
+        <v>0.05161750108172771</v>
       </c>
       <c r="J2">
-        <v>0.06022237758807943</v>
+        <v>0.03854367604495181</v>
       </c>
       <c r="K2">
-        <v>1337.468</v>
+        <v>1003.632</v>
       </c>
       <c r="L2">
-        <v>0.3078949609913649</v>
+        <v>0.2554485988444603</v>
       </c>
       <c r="M2">
-        <v>957.9231</v>
+        <v>683.7105</v>
       </c>
       <c r="N2">
-        <v>0.064423311274312</v>
+        <v>0.06346106722852875</v>
       </c>
       <c r="O2">
-        <v>0.7162213226783744</v>
+        <v>0.6812362499402171</v>
       </c>
       <c r="P2">
-        <v>935.3931</v>
+        <v>683.7105</v>
       </c>
       <c r="Q2">
-        <v>0.0629080986199661</v>
+        <v>0.06346106722852875</v>
       </c>
       <c r="R2">
-        <v>0.699376059838441</v>
+        <v>0.6812362499402171</v>
       </c>
       <c r="S2">
-        <v>22.53</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.02351963325657352</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1340.762</v>
+        <v>3804.66</v>
       </c>
       <c r="V2">
-        <v>0.09017041939041777</v>
+        <v>0.3531433026722482</v>
       </c>
       <c r="W2">
-        <v>0.06330902718896614</v>
+        <v>0.06752323674138874</v>
       </c>
       <c r="X2">
-        <v>0.03012531168979074</v>
+        <v>0.06562875848029903</v>
       </c>
       <c r="Y2">
-        <v>0.0331837154991754</v>
+        <v>0.00189447826108971</v>
       </c>
       <c r="Z2">
-        <v>0.2053689297130604</v>
+        <v>0.1931603184428945</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03057163129257626</v>
+        <v>0.06311351126579842</v>
       </c>
       <c r="AC2">
-        <v>-0.02829964134168783</v>
+        <v>-0.05900618397808198</v>
       </c>
       <c r="AD2">
-        <v>15118.261</v>
+        <v>18603.671</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15118.261</v>
+        <v>18603.671</v>
       </c>
       <c r="AG2">
-        <v>13777.499</v>
+        <v>14799.011</v>
       </c>
       <c r="AH2">
-        <v>0.5041527523787359</v>
+        <v>0.6332653456294643</v>
       </c>
       <c r="AI2">
-        <v>0.6693698534889891</v>
+        <v>0.7386882001288002</v>
       </c>
       <c r="AJ2">
-        <v>0.4809454310948706</v>
+        <v>0.5787032512900178</v>
       </c>
       <c r="AK2">
-        <v>0.6485039879173731</v>
+        <v>0.6921868537354934</v>
       </c>
       <c r="AL2">
-        <v>77.376</v>
+        <v>33.99</v>
       </c>
       <c r="AM2">
-        <v>75.849</v>
+        <v>23.109</v>
       </c>
       <c r="AN2">
-        <v>32.78027103209019</v>
+        <v>72.50066640685893</v>
       </c>
       <c r="AO2">
-        <v>4.361817617866005</v>
+        <v>5.966460723742277</v>
       </c>
       <c r="AP2">
-        <v>29.87315481352991</v>
+        <v>57.67346453624318</v>
       </c>
       <c r="AQ2">
-        <v>4.449630186291183</v>
+        <v>8.77580163572634</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gruppo MutuiOnline S.p.A (BIT:MOL)</t>
+          <t>doValue S.p.A. (BIT:DOV)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +725,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.183</v>
+        <v>0.253</v>
       </c>
       <c r="E3">
-        <v>0.446</v>
+        <v>0.0198</v>
       </c>
       <c r="G3">
-        <v>0.246875</v>
+        <v>0.2988389702170621</v>
       </c>
       <c r="H3">
-        <v>0.2245065789473684</v>
+        <v>0.2988389702170621</v>
       </c>
       <c r="I3">
-        <v>0.2338267543859649</v>
+        <v>0.2222783106175333</v>
       </c>
       <c r="J3">
-        <v>0.2338267543859649</v>
+        <v>0.1533286394281466</v>
       </c>
       <c r="K3">
-        <v>151</v>
+        <v>49.1</v>
       </c>
       <c r="L3">
-        <v>0.4139254385964912</v>
+        <v>0.08261820629311796</v>
       </c>
       <c r="M3">
-        <v>17.8176</v>
+        <v>36.7</v>
       </c>
       <c r="N3">
-        <v>0.009250610041015524</v>
+        <v>0.06063109202048572</v>
       </c>
       <c r="O3">
-        <v>0.1179973509933775</v>
+        <v>0.7474541751527495</v>
       </c>
       <c r="P3">
-        <v>17.8176</v>
+        <v>36.7</v>
       </c>
       <c r="Q3">
-        <v>0.009250610041015524</v>
+        <v>0.06063109202048572</v>
       </c>
       <c r="R3">
-        <v>0.1179973509933775</v>
+        <v>0.7474541751527495</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,73 +773,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>244.2</v>
+        <v>156.4</v>
       </c>
       <c r="V3">
-        <v>0.1267846944603084</v>
+        <v>0.2583842722616885</v>
       </c>
       <c r="W3">
-        <v>1.029311520109066</v>
+        <v>0.2984802431610942</v>
       </c>
       <c r="X3">
-        <v>0.02845786305511886</v>
+        <v>0.06562875848029903</v>
       </c>
       <c r="Y3">
-        <v>1.000853657053947</v>
+        <v>0.2328514846807952</v>
       </c>
       <c r="Z3">
-        <v>1.766585956416465</v>
+        <v>1.409295707849182</v>
       </c>
       <c r="AA3">
-        <v>0.4130750605326876</v>
+        <v>0.2160853934364418</v>
       </c>
       <c r="AB3">
-        <v>0.02887974475288415</v>
+        <v>0.06964714188915525</v>
       </c>
       <c r="AC3">
-        <v>0.3841953157798035</v>
+        <v>0.1464382515472866</v>
       </c>
       <c r="AD3">
-        <v>262.3</v>
+        <v>598.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>262.3</v>
+        <v>598.1</v>
       </c>
       <c r="AG3">
-        <v>18.10000000000002</v>
+        <v>441.7</v>
       </c>
       <c r="AH3">
-        <v>0.119859257905319</v>
+        <v>0.49700847598471</v>
       </c>
       <c r="AI3">
-        <v>0.4407662577718031</v>
+        <v>0.7501567791295624</v>
       </c>
       <c r="AJ3">
-        <v>0.009309741796111524</v>
+        <v>0.4218720152817574</v>
       </c>
       <c r="AK3">
-        <v>0.05158164719293252</v>
+        <v>0.6891870806678109</v>
       </c>
       <c r="AL3">
-        <v>3.63</v>
+        <v>31.3</v>
       </c>
       <c r="AM3">
-        <v>2.986</v>
+        <v>22.5</v>
       </c>
       <c r="AN3">
-        <v>2.967194570135747</v>
+        <v>3.28085573230938</v>
       </c>
       <c r="AO3">
-        <v>23.49862258953168</v>
+        <v>4.220447284345048</v>
       </c>
       <c r="AP3">
-        <v>0.2047511312217197</v>
+        <v>2.422929237520571</v>
       </c>
       <c r="AQ3">
-        <v>28.56664434025452</v>
+        <v>5.871111111111111</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cerved Group S.p.A. (BIT:CERV)</t>
+          <t>Gruppo MutuiOnline S.p.A (BIT:MOL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,121 +859,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.06150000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="E4">
-        <v>0.141</v>
+        <v>-0.033</v>
       </c>
       <c r="G4">
-        <v>0.3669852302345786</v>
+        <v>0.2767539605560944</v>
       </c>
       <c r="H4">
-        <v>0.3669852302345786</v>
+        <v>0.2767539605560944</v>
       </c>
       <c r="I4">
-        <v>0.2472632493483927</v>
+        <v>0.2285806660200453</v>
       </c>
       <c r="J4">
-        <v>0.2472632493483927</v>
+        <v>0.1142903330100226</v>
       </c>
       <c r="K4">
-        <v>88.59999999999999</v>
+        <v>21.9</v>
       </c>
       <c r="L4">
-        <v>0.1539530842745439</v>
+        <v>0.0708050436469447</v>
       </c>
       <c r="M4">
-        <v>17.2</v>
+        <v>14.7784</v>
       </c>
       <c r="N4">
-        <v>0.007626479847470402</v>
+        <v>0.01394057164418451</v>
       </c>
       <c r="O4">
-        <v>0.1941309255079007</v>
+        <v>0.6748127853881279</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>14.7784</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.01394057164418451</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.6748127853881279</v>
       </c>
       <c r="S4">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>107.3</v>
+        <v>214.6</v>
       </c>
       <c r="V4">
-        <v>0.04757681904846361</v>
+        <v>0.2024337326667296</v>
       </c>
       <c r="W4">
-        <v>0.1529960283198066</v>
+        <v>0.06691109074243812</v>
       </c>
       <c r="X4">
-        <v>0.03012531168979074</v>
+        <v>0.0579472134906466</v>
       </c>
       <c r="Y4">
-        <v>0.1228707166300158</v>
+        <v>0.008963877251791513</v>
       </c>
       <c r="Z4">
-        <v>1.457700101317122</v>
+        <v>0.8954834973943253</v>
       </c>
       <c r="AA4">
-        <v>0.3604356636271528</v>
+        <v>0.1023451071221772</v>
       </c>
       <c r="AB4">
-        <v>0.03057163129257626</v>
+        <v>0.05900807887664909</v>
       </c>
       <c r="AC4">
-        <v>0.3298640323345766</v>
+        <v>0.04333702824552808</v>
       </c>
       <c r="AD4">
-        <v>715.9</v>
+        <v>348.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>715.9</v>
+        <v>348.2</v>
       </c>
       <c r="AG4">
-        <v>608.6</v>
+        <v>133.6</v>
       </c>
       <c r="AH4">
-        <v>0.2409464189553042</v>
+        <v>0.2472484555847476</v>
       </c>
       <c r="AI4">
-        <v>0.5064374646293153</v>
+        <v>0.5768721007289596</v>
       </c>
       <c r="AJ4">
-        <v>0.212507419951814</v>
+        <v>0.11192091815364</v>
       </c>
       <c r="AK4">
-        <v>0.4658960422567557</v>
+        <v>0.3434447300771208</v>
       </c>
       <c r="AL4">
-        <v>42.5</v>
+        <v>2.69</v>
       </c>
       <c r="AM4">
-        <v>42.5</v>
+        <v>2.49</v>
       </c>
       <c r="AN4">
-        <v>3.487092060399415</v>
+        <v>4.686406460296097</v>
       </c>
       <c r="AO4">
-        <v>3.348235294117647</v>
+        <v>26.2825278810409</v>
       </c>
       <c r="AP4">
-        <v>2.964442279590842</v>
+        <v>1.798115746971736</v>
       </c>
       <c r="AQ4">
-        <v>3.348235294117647</v>
+        <v>28.39357429718876</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>doValue S.p.A. (BIT:DOV)</t>
+          <t>Confinvest F.L. S.p.A. (BIT:CFV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,115 +993,100 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.1627017135252038</v>
+        <v>0.004800884955752212</v>
       </c>
       <c r="H5">
-        <v>0.1627017135252038</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.1828314756280153</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.09141573781400765</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>8.31</v>
+        <v>0.593</v>
       </c>
       <c r="L5">
-        <v>0.01382465479953419</v>
+        <v>0.01311946902654867</v>
       </c>
       <c r="M5">
-        <v>30.83</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.04106833621952843</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>3.709987966305655</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>25.5</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03396829625682696</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>3.068592057761732</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>5.329999999999998</v>
-      </c>
-      <c r="T5">
-        <v>0.1728835549789166</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>160</v>
+        <v>1.59</v>
       </c>
       <c r="V5">
-        <v>0.2131344078859731</v>
+        <v>0.116058394160584</v>
       </c>
       <c r="W5">
-        <v>0.03592736705577172</v>
+        <v>0.08179310344827585</v>
       </c>
       <c r="X5">
-        <v>0.03568300832866393</v>
+        <v>0.05422516466182375</v>
       </c>
       <c r="Y5">
-        <v>0.0002443587271077907</v>
+        <v>0.0275679387864521</v>
       </c>
       <c r="Z5">
-        <v>1.763273687298328</v>
+        <v>8.934572049812216</v>
       </c>
       <c r="AA5">
-        <v>0.1611909650924025</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0387463565967076</v>
+        <v>0.05424408144533508</v>
       </c>
       <c r="AC5">
-        <v>0.1224446084956949</v>
+        <v>-0.05424408144533508</v>
       </c>
       <c r="AD5">
-        <v>691.8</v>
+        <v>0.121</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>691.8</v>
+        <v>0.121</v>
       </c>
       <c r="AG5">
-        <v>531.8</v>
+        <v>-1.469</v>
       </c>
       <c r="AH5">
-        <v>0.4795840554592721</v>
+        <v>0.008754793430287244</v>
       </c>
       <c r="AI5">
-        <v>0.7752129090094128</v>
+        <v>0.01706388379636159</v>
       </c>
       <c r="AJ5">
-        <v>0.4146588693957114</v>
+        <v>-0.1201046521134821</v>
       </c>
       <c r="AK5">
-        <v>0.7261059530311305</v>
+        <v>-0.2670423559352845</v>
       </c>
       <c r="AL5">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>30.662</v>
-      </c>
-      <c r="AN5">
-        <v>4.130149253731343</v>
-      </c>
-      <c r="AO5">
-        <v>3.522435897435898</v>
-      </c>
-      <c r="AP5">
-        <v>3.174925373134328</v>
-      </c>
-      <c r="AQ5">
-        <v>3.584241080164373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1112,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A. (BIT:CFV)</t>
+          <t>Conafi S.p.A. (BIT:CNF)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1120,8 +1105,11 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.377</v>
+      </c>
       <c r="G6">
-        <v>0.005660377358490566</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1133,28 +1121,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0.102</v>
+        <v>-5.3</v>
       </c>
       <c r="L6">
-        <v>0.00240566037735849</v>
+        <v>-3.3125</v>
       </c>
       <c r="M6">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="N6">
-        <v>0.06045454545454546</v>
+        <v>0.09166666666666666</v>
       </c>
       <c r="O6">
-        <v>13.03921568627451</v>
+        <v>-0.290566037735849</v>
       </c>
       <c r="P6">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="Q6">
-        <v>0.06045454545454546</v>
+        <v>0.09166666666666666</v>
       </c>
       <c r="R6">
-        <v>13.03921568627451</v>
+        <v>-0.290566037735849</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1163,61 +1151,64 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.492</v>
+        <v>9.07</v>
       </c>
       <c r="V6">
-        <v>0.02236363636363636</v>
+        <v>0.5398809523809524</v>
       </c>
       <c r="W6">
-        <v>0.01349206349206349</v>
+        <v>-0.3063583815028901</v>
       </c>
       <c r="X6">
-        <v>0.02735179386093799</v>
+        <v>0.05505807068758107</v>
       </c>
       <c r="Y6">
-        <v>-0.01385973036887449</v>
+        <v>-0.3614164521904712</v>
       </c>
       <c r="Z6">
-        <v>9.51312542068656</v>
+        <v>0.1271860095389507</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.02742443863097553</v>
+        <v>0.05580691742770413</v>
       </c>
       <c r="AC6">
-        <v>-0.02742443863097553</v>
+        <v>-0.05580691742770413</v>
       </c>
       <c r="AD6">
-        <v>0.351</v>
+        <v>1.35</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.351</v>
+        <v>1.35</v>
       </c>
       <c r="AG6">
-        <v>-0.141</v>
+        <v>-7.720000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.01570399534696434</v>
+        <v>0.0743801652892562</v>
       </c>
       <c r="AI6">
-        <v>0.04617813445599263</v>
+        <v>0.05908096280087528</v>
       </c>
       <c r="AJ6">
-        <v>-0.006450432316208426</v>
+        <v>-0.8502202643171807</v>
       </c>
       <c r="AK6">
-        <v>-0.01983401322267548</v>
+        <v>-0.5602322206095792</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>-0.171</v>
+      </c>
+      <c r="AQ6">
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conafi S.p.A. (BIT:CNF)</t>
+          <t>BFF Bank S.p.A. (BIT:BFF)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,7 +1228,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.336</v>
+        <v>0.164</v>
+      </c>
+      <c r="E7">
+        <v>-0.127</v>
+      </c>
+      <c r="F7">
+        <v>0.193</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1252,91 +1249,91 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-0.154</v>
+        <v>49.4</v>
       </c>
       <c r="L7">
-        <v>-0.08508287292817679</v>
+        <v>0.131803628601921</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>190.344</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.1300608131192347</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.853117408906883</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>190.344</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.1300608131192347</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>3.853117408906883</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>6.43</v>
+        <v>243.9</v>
       </c>
       <c r="V7">
-        <v>0.251171875</v>
+        <v>0.1666552784420909</v>
       </c>
       <c r="W7">
-        <v>-0.008749999999999999</v>
+        <v>0.05442326759942712</v>
       </c>
       <c r="X7">
-        <v>0.02781953370586977</v>
+        <v>0.06042419944596475</v>
       </c>
       <c r="Y7">
-        <v>-0.03656953370586977</v>
+        <v>-0.006000931846537633</v>
       </c>
       <c r="Z7">
-        <v>0.1594713656387665</v>
+        <v>0.6562773594817021</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.02829964134168783</v>
+        <v>0.05900618397808198</v>
       </c>
       <c r="AC7">
-        <v>-0.02829964134168783</v>
+        <v>-0.05900618397808198</v>
       </c>
       <c r="AD7">
-        <v>1.71</v>
+        <v>792</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.71</v>
+        <v>792</v>
       </c>
       <c r="AG7">
-        <v>-4.72</v>
+        <v>548.1</v>
       </c>
       <c r="AH7">
-        <v>0.06261442694983523</v>
+        <v>0.3511416537353137</v>
       </c>
       <c r="AI7">
-        <v>0.08995265649658074</v>
+        <v>0.5660781931241513</v>
       </c>
       <c r="AJ7">
-        <v>-0.2260536398467433</v>
+        <v>0.2724696758798966</v>
       </c>
       <c r="AK7">
-        <v>-0.3751987281399045</v>
+        <v>0.474463296398892</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.345</v>
-      </c>
-      <c r="AQ7">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1347,7 +1344,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BFF Bank S.p.A. (BIT:BFF)</t>
+          <t>illimity Bank S.p.A. (BIT:ILTY)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1356,7 +1353,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>0.11</v>
+        <v>0.43</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1371,10 +1368,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>319.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="L8">
-        <v>0.9707940371159113</v>
+        <v>0.2607373622196883</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1398,55 +1395,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>420.7</v>
+        <v>357</v>
       </c>
       <c r="V8">
-        <v>0.2836817262306136</v>
+        <v>0.5793573515092502</v>
       </c>
       <c r="W8">
-        <v>0.6369261477045909</v>
+        <v>0.07831944285877383</v>
       </c>
       <c r="X8">
-        <v>0.02853132636986393</v>
+        <v>0.07541471322432619</v>
       </c>
       <c r="Y8">
-        <v>0.608394821334727</v>
+        <v>0.002904729634447642</v>
       </c>
       <c r="Z8">
-        <v>0.2486384266263237</v>
+        <v>0.2163829262274858</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.02896557242889278</v>
+        <v>0.06311351126579842</v>
       </c>
       <c r="AC8">
-        <v>-0.02896557242889278</v>
+        <v>-0.06311351126579842</v>
       </c>
       <c r="AD8">
-        <v>213.8</v>
+        <v>1126.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>213.8</v>
+        <v>1126.7</v>
       </c>
       <c r="AG8">
-        <v>-206.9</v>
+        <v>769.7</v>
       </c>
       <c r="AH8">
-        <v>0.126001885902876</v>
+        <v>0.6464513167708991</v>
       </c>
       <c r="AI8">
-        <v>0.1906375390102541</v>
+        <v>0.5854811889420078</v>
       </c>
       <c r="AJ8">
-        <v>-0.1621346289475746</v>
+        <v>0.5553791759867234</v>
       </c>
       <c r="AK8">
-        <v>-0.2952340182648401</v>
+        <v>0.4910680107183871</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1463,7 +1460,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Banca Mediolanum S.p.A. (BIT:BMED)</t>
+          <t>Mittel S.p.A. (BIT:MIT)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1471,15 +1468,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.0595</v>
-      </c>
-      <c r="E9">
-        <v>0.0533</v>
-      </c>
-      <c r="F9">
-        <v>0.0897</v>
-      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1493,91 +1481,91 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>649.6</v>
+        <v>0.839</v>
       </c>
       <c r="L9">
-        <v>0.3931965377398463</v>
+        <v>0.004092682926829268</v>
       </c>
       <c r="M9">
-        <v>861.588</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.1190433292804244</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>1.326336206896552</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>861.588</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.1190433292804244</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>1.326336206896552</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>239.9</v>
+        <v>62.2</v>
       </c>
       <c r="V9">
-        <v>0.03314634685531116</v>
+        <v>0.6134122287968442</v>
       </c>
       <c r="W9">
-        <v>0.2205847397195151</v>
+        <v>0.003186479301177364</v>
       </c>
       <c r="X9">
-        <v>0.03633822013995891</v>
+        <v>0.09268619442553276</v>
       </c>
       <c r="Y9">
-        <v>0.1842465195795562</v>
+        <v>-0.08949971512435539</v>
       </c>
       <c r="Z9">
-        <v>0.1408968410998158</v>
+        <v>0.4624407850214301</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.03416586734327967</v>
+        <v>0.06480504351938617</v>
       </c>
       <c r="AC9">
-        <v>-0.03416586734327967</v>
+        <v>-0.06480504351938617</v>
       </c>
       <c r="AD9">
-        <v>7185.2</v>
+        <v>335.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>7185.2</v>
+        <v>335.8</v>
       </c>
       <c r="AG9">
-        <v>6945.3</v>
+        <v>273.6</v>
       </c>
       <c r="AH9">
-        <v>0.498183431788557</v>
+        <v>0.7680695333943275</v>
       </c>
       <c r="AI9">
-        <v>0.6946450496437444</v>
+        <v>0.5808683618751082</v>
       </c>
       <c r="AJ9">
-        <v>0.4896953373428565</v>
+        <v>0.7296</v>
       </c>
       <c r="AK9">
-        <v>0.6873948415447654</v>
+        <v>0.5303353363054855</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-1.71</v>
+      </c>
+      <c r="AQ9">
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -1588,7 +1576,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mittel S.p.A (BIT:MIT)</t>
+          <t>Banca Mediolanum S.p.A. (BIT:BMED)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1596,6 +1584,15 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.112</v>
+      </c>
+      <c r="E10">
+        <v>0.14</v>
+      </c>
+      <c r="F10">
+        <v>0.08</v>
+      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1609,93 +1606,90 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>8.91</v>
+        <v>695</v>
       </c>
       <c r="L10">
-        <v>0.04059225512528474</v>
+        <v>0.4435792698493745</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>340.2641</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.05531940041294771</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.4895886330935252</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>340.2641</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.05531940041294771</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.4895886330935252</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>158.7</v>
+        <v>2496.4</v>
       </c>
       <c r="V10">
-        <v>1.172082717872969</v>
+        <v>0.4058593051423369</v>
       </c>
       <c r="W10">
-        <v>0.03683340223232741</v>
+        <v>0.2200411587779009</v>
       </c>
       <c r="X10">
-        <v>0.0579707064804588</v>
+        <v>0.07406749571533222</v>
       </c>
       <c r="Y10">
-        <v>-0.02113730424813139</v>
+        <v>0.1459736630625687</v>
       </c>
       <c r="Z10">
-        <v>0.5454771371769384</v>
+        <v>0.1574720845854649</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.03796110774491654</v>
+        <v>0.06842200760039599</v>
       </c>
       <c r="AC10">
-        <v>-0.03796110774491654</v>
+        <v>-0.06842200760039599</v>
       </c>
       <c r="AD10">
-        <v>452.8</v>
+        <v>10535.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>452.8</v>
+        <v>10535.1</v>
       </c>
       <c r="AG10">
-        <v>294.1</v>
+        <v>8038.700000000001</v>
       </c>
       <c r="AH10">
-        <v>0.7698061883713022</v>
+        <v>0.6313736066163251</v>
       </c>
       <c r="AI10">
-        <v>0.6139661016949153</v>
+        <v>0.7858085882431918</v>
       </c>
       <c r="AJ10">
-        <v>0.6847497089639116</v>
+        <v>0.5665205502621639</v>
       </c>
       <c r="AK10">
-        <v>0.5081202487906014</v>
+        <v>0.736799171425167</v>
       </c>
       <c r="AL10">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>0.046</v>
-      </c>
-      <c r="AO10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
         <v>0</v>
       </c>
     </row>
@@ -1716,10 +1710,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.109</v>
+        <v>0.0443</v>
       </c>
       <c r="E11">
-        <v>0.04</v>
+        <v>-0.306</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1734,28 +1728,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>112</v>
+        <v>123.5</v>
       </c>
       <c r="L11">
-        <v>0.2007168458781362</v>
+        <v>0.2171237693389592</v>
       </c>
       <c r="M11">
-        <v>29.1575</v>
+        <v>100.084</v>
       </c>
       <c r="N11">
-        <v>0.02821238509917755</v>
+        <v>0.1341968356127648</v>
       </c>
       <c r="O11">
-        <v>0.2603348214285715</v>
+        <v>0.8103967611336031</v>
       </c>
       <c r="P11">
-        <v>29.1575</v>
+        <v>100.084</v>
       </c>
       <c r="Q11">
-        <v>0.02821238509917755</v>
+        <v>0.1341968356127648</v>
       </c>
       <c r="R11">
-        <v>0.2603348214285715</v>
+        <v>0.8103967611336031</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1764,55 +1758,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>3.04</v>
+        <v>263.5</v>
       </c>
       <c r="V11">
-        <v>0.002941461054668602</v>
+        <v>0.3533118798605525</v>
       </c>
       <c r="W11">
-        <v>0.06330902718896614</v>
+        <v>0.06752323674138874</v>
       </c>
       <c r="X11">
-        <v>0.07700416852353098</v>
+        <v>0.1301049725734927</v>
       </c>
       <c r="Y11">
-        <v>-0.01369514133456484</v>
+        <v>-0.062581735832104</v>
       </c>
       <c r="Z11">
-        <v>0.08274350166940203</v>
+        <v>0.07712165914612981</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03899873215602268</v>
+        <v>0.07125685159758655</v>
       </c>
       <c r="AC11">
-        <v>-0.03899873215602268</v>
+        <v>-0.07125685159758655</v>
       </c>
       <c r="AD11">
-        <v>5594.4</v>
+        <v>4866.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>5594.4</v>
+        <v>4866.3</v>
       </c>
       <c r="AG11">
-        <v>5591.36</v>
+        <v>4602.8</v>
       </c>
       <c r="AH11">
-        <v>0.8440682569139546</v>
+        <v>0.867108568984872</v>
       </c>
       <c r="AI11">
-        <v>0.7503822732516029</v>
+        <v>0.7549801414918704</v>
       </c>
       <c r="AJ11">
-        <v>0.8439967033265608</v>
+        <v>0.8605616422989193</v>
       </c>
       <c r="AK11">
-        <v>0.7502804480728252</v>
+        <v>0.7445366461234856</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/research/traditional_assets/database/data/italy/italy_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.134</v>
+        <v>0.1755</v>
       </c>
       <c r="E2">
-        <v>-0.033</v>
+        <v>0.192</v>
       </c>
       <c r="F2">
-        <v>0.193</v>
+        <v>0.148</v>
       </c>
       <c r="G2">
-        <v>0.06704599251698948</v>
+        <v>0.1635062861280351</v>
       </c>
       <c r="H2">
-        <v>0.06699076077273537</v>
+        <v>0.1634910475894941</v>
       </c>
       <c r="I2">
-        <v>0.05161750108172771</v>
+        <v>0.07421999462495187</v>
       </c>
       <c r="J2">
-        <v>0.03854367604495181</v>
+        <v>0.05442597777109891</v>
       </c>
       <c r="K2">
-        <v>1003.632</v>
+        <v>1482.663</v>
       </c>
       <c r="L2">
-        <v>0.2554485988444603</v>
+        <v>0.136931013750703</v>
       </c>
       <c r="M2">
-        <v>683.7105</v>
+        <v>766.93504</v>
       </c>
       <c r="N2">
-        <v>0.06346106722852875</v>
+        <v>0.03307750539118434</v>
       </c>
       <c r="O2">
-        <v>0.6812362499402171</v>
+        <v>0.5172686173459511</v>
       </c>
       <c r="P2">
-        <v>683.7105</v>
+        <v>761.76504</v>
       </c>
       <c r="Q2">
-        <v>0.06346106722852875</v>
+        <v>0.03285452600707323</v>
       </c>
       <c r="R2">
-        <v>0.6812362499402171</v>
+        <v>0.5137816482909467</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.006741118517677847</v>
       </c>
       <c r="U2">
-        <v>3804.66</v>
+        <v>3830.676</v>
       </c>
       <c r="V2">
-        <v>0.3531433026722482</v>
+        <v>0.1652150435607694</v>
       </c>
       <c r="W2">
-        <v>0.06752323674138874</v>
+        <v>0.1202960841264421</v>
       </c>
       <c r="X2">
-        <v>0.06562875848029903</v>
+        <v>0.07033636769149898</v>
       </c>
       <c r="Y2">
-        <v>0.00189447826108971</v>
+        <v>0.04995971643494311</v>
       </c>
       <c r="Z2">
-        <v>0.1931603184428945</v>
+        <v>0.3868952132668653</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06311351126579842</v>
+        <v>0.06321352097829665</v>
       </c>
       <c r="AC2">
-        <v>-0.05900618397808198</v>
+        <v>-0.0582977312794366</v>
       </c>
       <c r="AD2">
-        <v>18603.671</v>
+        <v>30973.178</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18603.671</v>
+        <v>30973.178</v>
       </c>
       <c r="AG2">
-        <v>14799.011</v>
+        <v>27142.502</v>
       </c>
       <c r="AH2">
-        <v>0.6332653456294643</v>
+        <v>0.5718915822540733</v>
       </c>
       <c r="AI2">
-        <v>0.7386882001288002</v>
+        <v>0.5914857177253041</v>
       </c>
       <c r="AJ2">
-        <v>0.5787032512900178</v>
+        <v>0.5393067729295817</v>
       </c>
       <c r="AK2">
-        <v>0.6921868537354934</v>
+        <v>0.5592428804889038</v>
       </c>
       <c r="AL2">
-        <v>33.99</v>
+        <v>409.644</v>
       </c>
       <c r="AM2">
-        <v>23.109</v>
+        <v>393.23</v>
       </c>
       <c r="AN2">
-        <v>72.50066640685893</v>
+        <v>16.64642893612447</v>
       </c>
       <c r="AO2">
-        <v>5.966460723742277</v>
+        <v>1.961800978410522</v>
       </c>
       <c r="AP2">
-        <v>57.67346453624318</v>
+        <v>14.58764517776046</v>
       </c>
       <c r="AQ2">
-        <v>8.77580163572634</v>
+        <v>2.04368944383694</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>doValue S.p.A. (BIT:DOV)</t>
+          <t>Gruppo MutuiOnline S.p.A (BIT:MOL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +725,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.253</v>
+        <v>0.179</v>
       </c>
       <c r="E3">
-        <v>0.0198</v>
+        <v>0.0434</v>
       </c>
       <c r="G3">
-        <v>0.2988389702170621</v>
+        <v>0.1923170435205446</v>
       </c>
       <c r="H3">
-        <v>0.2988389702170621</v>
+        <v>0.1923170435205446</v>
       </c>
       <c r="I3">
-        <v>0.2222783106175333</v>
+        <v>0.1760272307318259</v>
       </c>
       <c r="J3">
-        <v>0.1533286394281466</v>
+        <v>0.12757374213317</v>
       </c>
       <c r="K3">
-        <v>49.1</v>
+        <v>41</v>
       </c>
       <c r="L3">
-        <v>0.08261820629311796</v>
+        <v>0.09968392900559202</v>
       </c>
       <c r="M3">
-        <v>36.7</v>
+        <v>4.7498</v>
       </c>
       <c r="N3">
-        <v>0.06063109202048572</v>
+        <v>0.003602973526511416</v>
       </c>
       <c r="O3">
-        <v>0.7474541751527495</v>
+        <v>0.1158487804878049</v>
       </c>
       <c r="P3">
-        <v>36.7</v>
+        <v>4.7498</v>
       </c>
       <c r="Q3">
-        <v>0.06063109202048572</v>
+        <v>0.003602973526511416</v>
       </c>
       <c r="R3">
-        <v>0.7474541751527495</v>
+        <v>0.1158487804878049</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,73 +773,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>156.4</v>
+        <v>144.7</v>
       </c>
       <c r="V3">
-        <v>0.2583842722616885</v>
+        <v>0.1097625730106956</v>
       </c>
       <c r="W3">
-        <v>0.2984802431610942</v>
+        <v>0.1617357001972387</v>
       </c>
       <c r="X3">
-        <v>0.06562875848029903</v>
+        <v>0.0628187968603493</v>
       </c>
       <c r="Y3">
-        <v>0.2328514846807952</v>
+        <v>0.09891690333688935</v>
       </c>
       <c r="Z3">
-        <v>1.409295707849182</v>
+        <v>1.062516145698786</v>
       </c>
       <c r="AA3">
-        <v>0.2160853934364418</v>
+        <v>0.1355491607837066</v>
       </c>
       <c r="AB3">
-        <v>0.06964714188915525</v>
+        <v>0.06119713258173713</v>
       </c>
       <c r="AC3">
-        <v>0.1464382515472866</v>
+        <v>0.07435202820196947</v>
       </c>
       <c r="AD3">
-        <v>598.1</v>
+        <v>491.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>598.1</v>
+        <v>491.5</v>
       </c>
       <c r="AG3">
-        <v>441.7</v>
+        <v>346.8</v>
       </c>
       <c r="AH3">
-        <v>0.49700847598471</v>
+        <v>0.2715769698309206</v>
       </c>
       <c r="AI3">
-        <v>0.7501567791295624</v>
+        <v>0.5918121613485852</v>
       </c>
       <c r="AJ3">
-        <v>0.4218720152817574</v>
+        <v>0.2082757792324786</v>
       </c>
       <c r="AK3">
-        <v>0.6891870806678109</v>
+        <v>0.5056867891513561</v>
       </c>
       <c r="AL3">
-        <v>31.3</v>
+        <v>14.2</v>
       </c>
       <c r="AM3">
-        <v>22.5</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="AN3">
-        <v>3.28085573230938</v>
+        <v>6.159147869674186</v>
       </c>
       <c r="AO3">
-        <v>4.220447284345048</v>
+        <v>5.098591549295775</v>
       </c>
       <c r="AP3">
-        <v>2.422929237520571</v>
+        <v>4.345864661654136</v>
       </c>
       <c r="AQ3">
-        <v>5.871111111111111</v>
+        <v>10.05555555555556</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gruppo MutuiOnline S.p.A (BIT:MOL)</t>
+          <t>doValue S.p.A. (BIT:DOV)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,46 +859,43 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.156</v>
-      </c>
-      <c r="E4">
-        <v>-0.033</v>
+        <v>0.177</v>
       </c>
       <c r="G4">
-        <v>0.2767539605560944</v>
+        <v>0.3368272525700463</v>
       </c>
       <c r="H4">
-        <v>0.2767539605560944</v>
+        <v>0.3368272525700463</v>
       </c>
       <c r="I4">
-        <v>0.2285806660200453</v>
+        <v>0.1517839145333602</v>
       </c>
       <c r="J4">
-        <v>0.1142903330100226</v>
+        <v>0.0758919572666801</v>
       </c>
       <c r="K4">
-        <v>21.9</v>
+        <v>-17.9</v>
       </c>
       <c r="L4">
-        <v>0.0708050436469447</v>
+        <v>-0.03608143519451723</v>
       </c>
       <c r="M4">
-        <v>14.7784</v>
+        <v>52.9</v>
       </c>
       <c r="N4">
-        <v>0.01394057164418451</v>
+        <v>0.1779347460477632</v>
       </c>
       <c r="O4">
-        <v>0.6748127853881279</v>
+        <v>-2.955307262569832</v>
       </c>
       <c r="P4">
-        <v>14.7784</v>
+        <v>52.9</v>
       </c>
       <c r="Q4">
-        <v>0.01394057164418451</v>
+        <v>0.1779347460477632</v>
       </c>
       <c r="R4">
-        <v>0.6748127853881279</v>
+        <v>-2.955307262569832</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -907,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>214.6</v>
+        <v>101.3</v>
       </c>
       <c r="V4">
-        <v>0.2024337326667296</v>
+        <v>0.3407332660612176</v>
       </c>
       <c r="W4">
-        <v>0.06691109074243812</v>
+        <v>-0.1133628879037365</v>
       </c>
       <c r="X4">
-        <v>0.0579472134906466</v>
+        <v>0.08917389219731686</v>
       </c>
       <c r="Y4">
-        <v>0.008963877251791513</v>
+        <v>-0.2025367801010534</v>
       </c>
       <c r="Z4">
-        <v>0.8954834973943253</v>
+        <v>1.350667029676014</v>
       </c>
       <c r="AA4">
-        <v>0.1023451071221772</v>
+        <v>0.1025047644976858</v>
       </c>
       <c r="AB4">
-        <v>0.05900807887664909</v>
+        <v>0.07212553099663314</v>
       </c>
       <c r="AC4">
-        <v>0.04333702824552808</v>
+        <v>0.03037923350105266</v>
       </c>
       <c r="AD4">
-        <v>348.2</v>
+        <v>661.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>348.2</v>
+        <v>661.7</v>
       </c>
       <c r="AG4">
-        <v>133.6</v>
+        <v>560.4000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.2472484555847476</v>
+        <v>0.6899895724713243</v>
       </c>
       <c r="AI4">
-        <v>0.5768721007289596</v>
+        <v>0.824856644228372</v>
       </c>
       <c r="AJ4">
-        <v>0.11192091815364</v>
+        <v>0.6533753060510669</v>
       </c>
       <c r="AK4">
-        <v>0.3434447300771208</v>
+        <v>0.7995434441432444</v>
       </c>
       <c r="AL4">
-        <v>2.69</v>
+        <v>81.2</v>
       </c>
       <c r="AM4">
-        <v>2.49</v>
+        <v>79.16</v>
       </c>
       <c r="AN4">
-        <v>4.686406460296097</v>
+        <v>6.065077910174153</v>
       </c>
       <c r="AO4">
-        <v>26.2825278810409</v>
+        <v>0.9273399014778324</v>
       </c>
       <c r="AP4">
-        <v>1.798115746971736</v>
+        <v>5.136571952337306</v>
       </c>
       <c r="AQ4">
-        <v>28.39357429718876</v>
+        <v>0.9512379989893885</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A. (BIT:CFV)</t>
+          <t>Poligrafici Printing S.p.A. (BIT:POPR)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -992,23 +989,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.0184</v>
+      </c>
       <c r="G5">
-        <v>0.004800884955752212</v>
+        <v>0.2010869565217391</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.2010869565217391</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.1282608695652174</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.100650819450088</v>
       </c>
       <c r="K5">
-        <v>0.593</v>
+        <v>2.52</v>
       </c>
       <c r="L5">
-        <v>0.01311946902654867</v>
+        <v>0.09130434782608696</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1032,61 +1032,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.59</v>
+        <v>0.273</v>
       </c>
       <c r="V5">
-        <v>0.116058394160584</v>
+        <v>0.02353448275862069</v>
       </c>
       <c r="W5">
-        <v>0.08179310344827585</v>
+        <v>0.08659793814432989</v>
       </c>
       <c r="X5">
-        <v>0.05422516466182375</v>
+        <v>0.06956926589903147</v>
       </c>
       <c r="Y5">
-        <v>0.0275679387864521</v>
+        <v>0.01702867224529843</v>
       </c>
       <c r="Z5">
-        <v>8.934572049812216</v>
+        <v>0.7091834112749885</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.07137989148523639</v>
       </c>
       <c r="AB5">
-        <v>0.05424408144533508</v>
+        <v>0.0617076158533529</v>
       </c>
       <c r="AC5">
-        <v>-0.05424408144533508</v>
+        <v>0.009672275631883498</v>
       </c>
       <c r="AD5">
-        <v>0.121</v>
+        <v>9.83</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.121</v>
+        <v>9.83</v>
       </c>
       <c r="AG5">
-        <v>-1.469</v>
+        <v>9.557</v>
       </c>
       <c r="AH5">
-        <v>0.008754793430287244</v>
+        <v>0.45870275314979</v>
       </c>
       <c r="AI5">
-        <v>0.01706388379636159</v>
+        <v>0.228977405078034</v>
       </c>
       <c r="AJ5">
-        <v>-0.1201046521134821</v>
+        <v>0.4517181074821572</v>
       </c>
       <c r="AK5">
-        <v>-0.2670423559352845</v>
+        <v>0.2240429472302318</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.239</v>
+      </c>
+      <c r="AN5">
+        <v>2.160439560439561</v>
+      </c>
+      <c r="AO5">
+        <v>10.29069767441861</v>
+      </c>
+      <c r="AP5">
+        <v>2.100439560439561</v>
+      </c>
+      <c r="AQ5">
+        <v>14.81171548117155</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Conafi S.p.A. (BIT:CNF)</t>
+          <t>Nexi S.p.A. (BIT:NEXI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1105,110 +1117,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.377</v>
+      <c r="F6">
+        <v>0.148</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.2416723696146929</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.2416723696146929</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.1038307895532602</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.05191539477663011</v>
       </c>
       <c r="K6">
-        <v>-5.3</v>
+        <v>91</v>
       </c>
       <c r="L6">
-        <v>-3.3125</v>
+        <v>0.01448283545270797</v>
       </c>
       <c r="M6">
-        <v>1.54</v>
+        <v>5.17</v>
       </c>
       <c r="N6">
-        <v>0.09166666666666666</v>
+        <v>0.0004815304658830542</v>
       </c>
       <c r="O6">
-        <v>-0.290566037735849</v>
+        <v>0.05681318681318681</v>
       </c>
       <c r="P6">
-        <v>1.54</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.09166666666666666</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0.290566037735849</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>9.07</v>
+        <v>459.5</v>
       </c>
       <c r="V6">
-        <v>0.5398809523809524</v>
+        <v>0.04279753366987687</v>
       </c>
       <c r="W6">
-        <v>-0.3063583815028901</v>
+        <v>0.007076425394257986</v>
       </c>
       <c r="X6">
-        <v>0.05505807068758107</v>
+        <v>0.07110346948396651</v>
       </c>
       <c r="Y6">
-        <v>-0.3614164521904712</v>
+        <v>-0.06402704408970852</v>
       </c>
       <c r="Z6">
-        <v>0.1271860095389507</v>
+        <v>0.9080044509313719</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.04713940952903944</v>
       </c>
       <c r="AB6">
-        <v>0.05580691742770413</v>
+        <v>0.06613097420127613</v>
       </c>
       <c r="AC6">
-        <v>-0.05580691742770413</v>
+        <v>-0.01899156467223669</v>
       </c>
       <c r="AD6">
-        <v>1.35</v>
+        <v>10256.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.35</v>
+        <v>10256.4</v>
       </c>
       <c r="AG6">
-        <v>-7.720000000000001</v>
+        <v>9796.9</v>
       </c>
       <c r="AH6">
-        <v>0.0743801652892562</v>
+        <v>0.4885628542847616</v>
       </c>
       <c r="AI6">
-        <v>0.05908096280087528</v>
+        <v>0.4349378532990124</v>
       </c>
       <c r="AJ6">
-        <v>-0.8502202643171807</v>
+        <v>0.4771178805366839</v>
       </c>
       <c r="AK6">
-        <v>-0.5602322206095792</v>
+        <v>0.4237083618057418</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>313.9</v>
       </c>
       <c r="AM6">
-        <v>-0.171</v>
+        <v>313.9</v>
+      </c>
+      <c r="AN6">
+        <v>6.151871401151631</v>
+      </c>
+      <c r="AO6">
+        <v>2.078368907295317</v>
+      </c>
+      <c r="AP6">
+        <v>5.876259596928982</v>
       </c>
       <c r="AQ6">
-        <v>-0</v>
+        <v>2.078368907295317</v>
       </c>
     </row>
     <row r="7">
@@ -1228,13 +1249,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.164</v>
+        <v>0.184</v>
       </c>
       <c r="E7">
-        <v>-0.127</v>
+        <v>0.244</v>
       </c>
       <c r="F7">
-        <v>0.193</v>
+        <v>0.127</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1249,28 +1270,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>49.4</v>
+        <v>268.9</v>
       </c>
       <c r="L7">
-        <v>0.131803628601921</v>
+        <v>0.5986197684772929</v>
       </c>
       <c r="M7">
-        <v>190.344</v>
+        <v>168.9741</v>
       </c>
       <c r="N7">
-        <v>0.1300608131192347</v>
+        <v>0.07950599915306075</v>
       </c>
       <c r="O7">
-        <v>3.853117408906883</v>
+        <v>0.6283901078467833</v>
       </c>
       <c r="P7">
-        <v>190.344</v>
+        <v>168.9741</v>
       </c>
       <c r="Q7">
-        <v>0.1300608131192347</v>
+        <v>0.07950599915306075</v>
       </c>
       <c r="R7">
-        <v>3.853117408906883</v>
+        <v>0.6283901078467833</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1279,55 +1300,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>243.9</v>
+        <v>445.3</v>
       </c>
       <c r="V7">
-        <v>0.1666552784420909</v>
+        <v>0.2095233614078012</v>
       </c>
       <c r="W7">
-        <v>0.05442326759942712</v>
+        <v>0.4429253829682095</v>
       </c>
       <c r="X7">
-        <v>0.06042419944596475</v>
+        <v>0.05751965459508079</v>
       </c>
       <c r="Y7">
-        <v>-0.006000931846537633</v>
+        <v>0.3854057283731287</v>
       </c>
       <c r="Z7">
-        <v>0.6562773594817021</v>
+        <v>0.3993243843897236</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05900618397808198</v>
+        <v>0.057518242166999</v>
       </c>
       <c r="AC7">
-        <v>-0.05900618397808198</v>
+        <v>-0.057518242166999</v>
       </c>
       <c r="AD7">
-        <v>792</v>
+        <v>0.59</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>792</v>
+        <v>0.59</v>
       </c>
       <c r="AG7">
-        <v>548.1</v>
+        <v>-444.71</v>
       </c>
       <c r="AH7">
-        <v>0.3511416537353137</v>
+        <v>0.0002775308223849775</v>
       </c>
       <c r="AI7">
-        <v>0.5660781931241513</v>
+        <v>0.0007967697065456656</v>
       </c>
       <c r="AJ7">
-        <v>0.2724696758798966</v>
+        <v>-0.2646154029239731</v>
       </c>
       <c r="AK7">
-        <v>0.474463296398892</v>
+        <v>-1.506521223618687</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1344,7 +1365,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>illimity Bank S.p.A. (BIT:ILTY)</t>
+          <t>Confinvest F.L. S.p.A. (BIT:CFV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1352,11 +1373,14 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="F8">
-        <v>0.43</v>
+      <c r="D8">
+        <v>0.331</v>
+      </c>
+      <c r="E8">
+        <v>0.458</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.003409090909090909</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1368,82 +1392,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>68.59999999999999</v>
+        <v>0.485</v>
       </c>
       <c r="L8">
-        <v>0.2607373622196883</v>
+        <v>0.01002066115702479</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>0.7511399999999999</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.0605758064516129</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>1.548742268041237</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>0.7511399999999999</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.0605758064516129</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>1.548742268041237</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>357</v>
+        <v>0.753</v>
       </c>
       <c r="V8">
-        <v>0.5793573515092502</v>
+        <v>0.0607258064516129</v>
       </c>
       <c r="W8">
-        <v>0.07831944285877383</v>
+        <v>0.07049418604651163</v>
       </c>
       <c r="X8">
-        <v>0.07541471322432619</v>
+        <v>0.05854579422285865</v>
       </c>
       <c r="Y8">
-        <v>0.002904729634447642</v>
+        <v>0.01194839182365298</v>
       </c>
       <c r="Z8">
-        <v>0.2163829262274858</v>
+        <v>13.0212536992198</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06311351126579842</v>
+        <v>0.05813282731494665</v>
       </c>
       <c r="AC8">
-        <v>-0.06311351126579842</v>
+        <v>-0.05813282731494665</v>
       </c>
       <c r="AD8">
-        <v>1126.7</v>
+        <v>0.898</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1126.7</v>
+        <v>0.898</v>
       </c>
       <c r="AG8">
-        <v>769.7</v>
+        <v>0.145</v>
       </c>
       <c r="AH8">
-        <v>0.6464513167708991</v>
+        <v>0.06752895172206347</v>
       </c>
       <c r="AI8">
-        <v>0.5854811889420078</v>
+        <v>0.114133197763091</v>
       </c>
       <c r="AJ8">
-        <v>0.5553791759867234</v>
+        <v>0.01155838979673177</v>
       </c>
       <c r="AK8">
-        <v>0.4910680107183871</v>
+        <v>0.02037947997189037</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1460,7 +1487,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mittel S.p.A. (BIT:MIT)</t>
+          <t>Conafi S.p.A. (BIT:CNF)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1468,6 +1495,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.0108</v>
+      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1481,10 +1511,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0.839</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="L9">
-        <v>0.004092682926829268</v>
+        <v>-0.1621342512908778</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1493,7 +1523,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1502,67 +1532,67 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>62.2</v>
+        <v>6.35</v>
       </c>
       <c r="V9">
-        <v>0.6134122287968442</v>
+        <v>0.5825688073394495</v>
       </c>
       <c r="W9">
-        <v>0.003186479301177364</v>
+        <v>-0.05924528301886792</v>
       </c>
       <c r="X9">
-        <v>0.09268619442553276</v>
+        <v>0.05915994077964297</v>
       </c>
       <c r="Y9">
-        <v>-0.08949971512435539</v>
+        <v>-0.1184052237985109</v>
       </c>
       <c r="Z9">
-        <v>0.4624407850214301</v>
+        <v>0.7102689486552567</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06480504351938617</v>
+        <v>0.05846263524392657</v>
       </c>
       <c r="AC9">
-        <v>-0.06480504351938617</v>
+        <v>-0.05846263524392657</v>
       </c>
       <c r="AD9">
-        <v>335.8</v>
+        <v>1.26</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>335.8</v>
+        <v>1.26</v>
       </c>
       <c r="AG9">
-        <v>273.6</v>
+        <v>-5.09</v>
       </c>
       <c r="AH9">
-        <v>0.7680695333943275</v>
+        <v>0.1036184210526316</v>
       </c>
       <c r="AI9">
-        <v>0.5808683618751082</v>
+        <v>0.05585106382978723</v>
       </c>
       <c r="AJ9">
-        <v>0.7296</v>
+        <v>-0.8760757314974181</v>
       </c>
       <c r="AK9">
-        <v>0.5303353363054855</v>
+        <v>-0.3140037014188772</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1.71</v>
+        <v>-0.159</v>
       </c>
       <c r="AQ9">
         <v>-0</v>
@@ -1576,7 +1606,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Banca Mediolanum S.p.A. (BIT:BMED)</t>
+          <t>Mittel S.p.A. (BIT:MIT)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1585,13 +1615,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.112</v>
+        <v>0.174</v>
       </c>
       <c r="E10">
-        <v>0.14</v>
-      </c>
-      <c r="F10">
-        <v>0.08</v>
+        <v>0.597</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1606,91 +1633,91 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>695</v>
+        <v>49.8</v>
       </c>
       <c r="L10">
-        <v>0.4435792698493745</v>
+        <v>0.2472691161866931</v>
       </c>
       <c r="M10">
-        <v>340.2641</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.05531940041294771</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.4895886330935252</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>340.2641</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.05531940041294771</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.4895886330935252</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>2496.4</v>
+        <v>118.9</v>
       </c>
       <c r="V10">
-        <v>0.4058593051423369</v>
+        <v>0.8697878566203366</v>
       </c>
       <c r="W10">
-        <v>0.2200411587779009</v>
+        <v>0.2169934640522876</v>
       </c>
       <c r="X10">
-        <v>0.07406749571533222</v>
+        <v>0.06298885193006991</v>
       </c>
       <c r="Y10">
-        <v>0.1459736630625687</v>
+        <v>0.1540046121222177</v>
       </c>
       <c r="Z10">
-        <v>0.1574720845854649</v>
+        <v>0.5003726708074534</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06842200760039599</v>
+        <v>0.06005501593891419</v>
       </c>
       <c r="AC10">
-        <v>-0.06842200760039599</v>
+        <v>-0.06005501593891419</v>
       </c>
       <c r="AD10">
-        <v>10535.1</v>
+        <v>52.6</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>10535.1</v>
+        <v>52.6</v>
       </c>
       <c r="AG10">
-        <v>8038.700000000001</v>
+        <v>-66.30000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.6313736066163251</v>
+        <v>0.277865821447438</v>
       </c>
       <c r="AI10">
-        <v>0.7858085882431918</v>
+        <v>0.1497722095671982</v>
       </c>
       <c r="AJ10">
-        <v>0.5665205502621639</v>
+        <v>-0.9417613636363641</v>
       </c>
       <c r="AK10">
-        <v>0.736799171425167</v>
+        <v>-0.2854068015497202</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>-7.11</v>
+      </c>
+      <c r="AQ10">
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -1701,117 +1728,477 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>illimity Bank S.p.A. (BIT:ILTY)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>1.597</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>105.6</v>
+      </c>
+      <c r="L11">
+        <v>0.3248231313442018</v>
+      </c>
+      <c r="M11">
+        <v>16.0058</v>
+      </c>
+      <c r="N11">
+        <v>0.03166330365974283</v>
+      </c>
+      <c r="O11">
+        <v>0.1515700757575758</v>
+      </c>
+      <c r="P11">
+        <v>16.0058</v>
+      </c>
+      <c r="Q11">
+        <v>0.03166330365974283</v>
+      </c>
+      <c r="R11">
+        <v>0.1515700757575758</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>340.2</v>
+      </c>
+      <c r="V11">
+        <v>0.6729970326409496</v>
+      </c>
+      <c r="W11">
+        <v>0.132380594208349</v>
+      </c>
+      <c r="X11">
+        <v>0.1104720827516746</v>
+      </c>
+      <c r="Y11">
+        <v>0.02190851145667436</v>
+      </c>
+      <c r="Z11">
+        <v>0.2162575666866227</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.0647194261032404</v>
+      </c>
+      <c r="AC11">
+        <v>-0.0647194261032404</v>
+      </c>
+      <c r="AD11">
+        <v>1882</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>1882</v>
+      </c>
+      <c r="AG11">
+        <v>1541.8</v>
+      </c>
+      <c r="AH11">
+        <v>0.7882722513089006</v>
+      </c>
+      <c r="AI11">
+        <v>0.6583642342405374</v>
+      </c>
+      <c r="AJ11">
+        <v>0.7530894348654326</v>
+      </c>
+      <c r="AK11">
+        <v>0.6122141041931385</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Banca IFIS S.p.A. (BIT:IF)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.0443</v>
-      </c>
-      <c r="E11">
-        <v>-0.306</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>123.5</v>
-      </c>
-      <c r="L11">
-        <v>0.2171237693389592</v>
-      </c>
-      <c r="M11">
-        <v>100.084</v>
-      </c>
-      <c r="N11">
-        <v>0.1341968356127648</v>
-      </c>
-      <c r="O11">
-        <v>0.8103967611336031</v>
-      </c>
-      <c r="P11">
-        <v>100.084</v>
-      </c>
-      <c r="Q11">
-        <v>0.1341968356127648</v>
-      </c>
-      <c r="R11">
-        <v>0.8103967611336031</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>263.5</v>
-      </c>
-      <c r="V11">
-        <v>0.3533118798605525</v>
-      </c>
-      <c r="W11">
-        <v>0.06752323674138874</v>
-      </c>
-      <c r="X11">
-        <v>0.1301049725734927</v>
-      </c>
-      <c r="Y11">
-        <v>-0.062581735832104</v>
-      </c>
-      <c r="Z11">
-        <v>0.07712165914612981</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.07125685159758655</v>
-      </c>
-      <c r="AC11">
-        <v>-0.07125685159758655</v>
-      </c>
-      <c r="AD11">
-        <v>4866.3</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>4866.3</v>
-      </c>
-      <c r="AG11">
-        <v>4602.8</v>
-      </c>
-      <c r="AH11">
-        <v>0.867108568984872</v>
-      </c>
-      <c r="AI11">
-        <v>0.7549801414918704</v>
-      </c>
-      <c r="AJ11">
-        <v>0.8605616422989193</v>
-      </c>
-      <c r="AK11">
-        <v>0.7445366461234856</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
+      <c r="D12">
+        <v>0.07629999999999999</v>
+      </c>
+      <c r="E12">
+        <v>0.0585</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>169.6</v>
+      </c>
+      <c r="L12">
+        <v>0.2491552813280446</v>
+      </c>
+      <c r="M12">
+        <v>88.72499999999999</v>
+      </c>
+      <c r="N12">
+        <v>0.09744645799011531</v>
+      </c>
+      <c r="O12">
+        <v>0.5231426886792453</v>
+      </c>
+      <c r="P12">
+        <v>88.72499999999999</v>
+      </c>
+      <c r="Q12">
+        <v>0.09744645799011531</v>
+      </c>
+      <c r="R12">
+        <v>0.5231426886792453</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>1537.9</v>
+      </c>
+      <c r="V12">
+        <v>1.689071938495332</v>
+      </c>
+      <c r="W12">
+        <v>0.1082115740445352</v>
+      </c>
+      <c r="X12">
+        <v>0.1644444024014277</v>
+      </c>
+      <c r="Y12">
+        <v>-0.0562328283568925</v>
+      </c>
+      <c r="Z12">
+        <v>0.1109933472475867</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.06558140493912271</v>
+      </c>
+      <c r="AC12">
+        <v>-0.06558140493912271</v>
+      </c>
+      <c r="AD12">
+        <v>6844.7</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>6844.7</v>
+      </c>
+      <c r="AG12">
+        <v>5306.799999999999</v>
+      </c>
+      <c r="AH12">
+        <v>0.8825949040643697</v>
+      </c>
+      <c r="AI12">
+        <v>0.7913496889957685</v>
+      </c>
+      <c r="AJ12">
+        <v>0.8535537934473163</v>
+      </c>
+      <c r="AK12">
+        <v>0.7462279406594952</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Banca Mediolanum S.p.A. (BIT:BMED)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.113</v>
+      </c>
+      <c r="E13">
+        <v>0.14</v>
+      </c>
+      <c r="F13">
+        <v>0.158</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>758.7</v>
+      </c>
+      <c r="L13">
+        <v>0.4078374455732947</v>
+      </c>
+      <c r="M13">
+        <v>423.9092</v>
+      </c>
+      <c r="N13">
+        <v>0.06063641825203833</v>
+      </c>
+      <c r="O13">
+        <v>0.5587309872149729</v>
+      </c>
+      <c r="P13">
+        <v>423.9092</v>
+      </c>
+      <c r="Q13">
+        <v>0.06063641825203833</v>
+      </c>
+      <c r="R13">
+        <v>0.5587309872149729</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>590.5</v>
+      </c>
+      <c r="V13">
+        <v>0.08446574166785868</v>
+      </c>
+      <c r="W13">
+        <v>0.2642081069786879</v>
+      </c>
+      <c r="X13">
+        <v>0.07887032904842466</v>
+      </c>
+      <c r="Y13">
+        <v>0.1853377779302632</v>
+      </c>
+      <c r="Z13">
+        <v>0.172569573283859</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.06686949325472528</v>
+      </c>
+      <c r="AC13">
+        <v>-0.06686949325472528</v>
+      </c>
+      <c r="AD13">
+        <v>10495.7</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>10495.7</v>
+      </c>
+      <c r="AG13">
+        <v>9905.200000000001</v>
+      </c>
+      <c r="AH13">
+        <v>0.600210445652982</v>
+      </c>
+      <c r="AI13">
+        <v>0.742464435531221</v>
+      </c>
+      <c r="AJ13">
+        <v>0.5862383257773938</v>
+      </c>
+      <c r="AK13">
+        <v>0.7312377268230743</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A. (BIT:GF)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>13.9</v>
+      </c>
+      <c r="L14">
+        <v>0.3601036269430052</v>
+      </c>
+      <c r="M14">
+        <v>5.75</v>
+      </c>
+      <c r="N14">
+        <v>0.04426481909160893</v>
+      </c>
+      <c r="O14">
+        <v>0.4136690647482014</v>
+      </c>
+      <c r="P14">
+        <v>5.75</v>
+      </c>
+      <c r="Q14">
+        <v>0.04426481909160893</v>
+      </c>
+      <c r="R14">
+        <v>0.4136690647482014</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>85</v>
+      </c>
+      <c r="V14">
+        <v>0.6543494996150885</v>
+      </c>
+      <c r="W14">
+        <v>0.2607879924953096</v>
+      </c>
+      <c r="X14">
+        <v>0.08773746475940168</v>
+      </c>
+      <c r="Y14">
+        <v>0.1730505277359079</v>
+      </c>
+      <c r="Z14">
+        <v>0.1214600377595972</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.06811248726406337</v>
+      </c>
+      <c r="AC14">
+        <v>-0.06811248726406337</v>
+      </c>
+      <c r="AD14">
+        <v>276</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>276</v>
+      </c>
+      <c r="AG14">
+        <v>191</v>
+      </c>
+      <c r="AH14">
+        <v>0.6799704360679971</v>
+      </c>
+      <c r="AI14">
+        <v>0.8077260755048288</v>
+      </c>
+      <c r="AJ14">
+        <v>0.595200997195388</v>
+      </c>
+      <c r="AK14">
+        <v>0.7440592130892092</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/italy/italy_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2265</v>
+        <v>0.159</v>
       </c>
       <c r="E2">
-        <v>0.281</v>
+        <v>0.0333</v>
       </c>
       <c r="F2">
-        <v>0.10315</v>
+        <v>0.15</v>
       </c>
       <c r="G2">
-        <v>0.1614084760235495</v>
+        <v>0.1341156460476931</v>
       </c>
       <c r="H2">
-        <v>0.1614084760235495</v>
+        <v>0.1340943078316565</v>
       </c>
       <c r="I2">
-        <v>0.09355759291717228</v>
+        <v>0.07965086782790241</v>
       </c>
       <c r="J2">
-        <v>0.08250066044066888</v>
+        <v>0.06354217065494004</v>
       </c>
       <c r="K2">
-        <v>-115.4000000000001</v>
+        <v>473.6139999999999</v>
       </c>
       <c r="L2">
-        <v>-0.01296570940631883</v>
+        <v>0.0419339329873768</v>
       </c>
       <c r="M2">
-        <v>779.4094</v>
+        <v>1133.8024</v>
       </c>
       <c r="N2">
-        <v>0.04993557274014467</v>
+        <v>0.05510234590281052</v>
       </c>
       <c r="O2">
-        <v>-6.753980935875211</v>
+        <v>2.393937679207118</v>
       </c>
       <c r="P2">
-        <v>653.0094</v>
+        <v>1006.9164</v>
       </c>
       <c r="Q2">
-        <v>0.04183731732475671</v>
+        <v>0.04893573674567343</v>
       </c>
       <c r="R2">
-        <v>-5.658660311958402</v>
+        <v>2.126027524524191</v>
       </c>
       <c r="S2">
-        <v>126.4</v>
+        <v>126.886</v>
       </c>
       <c r="T2">
-        <v>0.1621740769356901</v>
+        <v>0.1119119169266179</v>
       </c>
       <c r="U2">
-        <v>711.9</v>
+        <v>2436.713</v>
       </c>
       <c r="V2">
-        <v>0.04561034834030612</v>
+        <v>0.1184232830975443</v>
       </c>
       <c r="W2">
-        <v>0.0984689642351908</v>
+        <v>0.08510267348640477</v>
       </c>
       <c r="X2">
-        <v>0.07721096871226901</v>
+        <v>0.07244484985609109</v>
       </c>
       <c r="Y2">
-        <v>0.02125799552292179</v>
+        <v>0.01265782363031367</v>
       </c>
       <c r="Z2">
-        <v>0.4483896482062701</v>
+        <v>0.3676477744811276</v>
       </c>
       <c r="AA2">
-        <v>0.06468175674625987</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06929239039102332</v>
+        <v>0.06627904082493555</v>
       </c>
       <c r="AC2">
-        <v>-0.004610633644763454</v>
+        <v>-0.06500015332635145</v>
       </c>
       <c r="AD2">
-        <v>16478</v>
+        <v>25334.189</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>16478</v>
+        <v>25334.189</v>
       </c>
       <c r="AG2">
-        <v>15766.1</v>
+        <v>22897.476</v>
       </c>
       <c r="AH2">
-        <v>0.5135525130663243</v>
+        <v>0.5518170150616344</v>
       </c>
       <c r="AI2">
-        <v>0.5029239052141958</v>
+        <v>0.5460999765925025</v>
       </c>
       <c r="AJ2">
-        <v>0.5025147891274415</v>
+        <v>0.5266962777744451</v>
       </c>
       <c r="AK2">
-        <v>0.49188362842212</v>
+        <v>0.5209369909355618</v>
       </c>
       <c r="AL2">
-        <v>479.5</v>
+        <v>499</v>
       </c>
       <c r="AM2">
-        <v>479.5</v>
+        <v>483.662</v>
       </c>
       <c r="AN2">
-        <v>12.98707440100883</v>
+        <v>18.83022818492642</v>
       </c>
       <c r="AO2">
-        <v>1.736600625651721</v>
+        <v>1.802805611222445</v>
       </c>
       <c r="AP2">
-        <v>12.42599306431274</v>
+        <v>17.01908428720084</v>
       </c>
       <c r="AQ2">
-        <v>1.736600625651721</v>
+        <v>1.859976595225592</v>
       </c>
     </row>
     <row r="3">
@@ -782,10 +782,10 @@
         <v>-0.08614727726493671</v>
       </c>
       <c r="X3">
-        <v>0.07758300658054471</v>
+        <v>0.07757705370070694</v>
       </c>
       <c r="Y3">
-        <v>-0.1637302838454814</v>
+        <v>-0.1637243309656436</v>
       </c>
       <c r="Z3">
         <v>1.020413553107863</v>
@@ -794,10 +794,10 @@
         <v>0.1293635134925197</v>
       </c>
       <c r="AB3">
-        <v>0.07005484969168888</v>
+        <v>0.07005199779066321</v>
       </c>
       <c r="AC3">
-        <v>0.05930866380083086</v>
+        <v>0.05931151570185653</v>
       </c>
       <c r="AD3">
         <v>7433.8</v>
@@ -850,120 +850,1105 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Moltiply Group S.p.A. (BIT:MOL)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.159</v>
+      </c>
+      <c r="E4">
+        <v>-0.0184</v>
+      </c>
+      <c r="G4">
+        <v>0.1554890219560878</v>
+      </c>
+      <c r="H4">
+        <v>0.1554890219560878</v>
+      </c>
+      <c r="I4">
+        <v>0.1335329341317365</v>
+      </c>
+      <c r="J4">
+        <v>0.09251924721984602</v>
+      </c>
+      <c r="K4">
+        <v>37.7</v>
+      </c>
+      <c r="L4">
+        <v>0.075249500998004</v>
+      </c>
+      <c r="M4">
+        <v>5.0116</v>
+      </c>
+      <c r="N4">
+        <v>0.00355962781447546</v>
+      </c>
+      <c r="O4">
+        <v>0.1329336870026525</v>
+      </c>
+      <c r="P4">
+        <v>5.0116</v>
+      </c>
+      <c r="Q4">
+        <v>0.00355962781447546</v>
+      </c>
+      <c r="R4">
+        <v>0.1329336870026525</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>142.8</v>
+      </c>
+      <c r="V4">
+        <v>0.1014276582143618</v>
+      </c>
+      <c r="W4">
+        <v>0.112035661218425</v>
+      </c>
+      <c r="X4">
+        <v>0.0680565823844507</v>
+      </c>
+      <c r="Y4">
+        <v>0.04397907883397427</v>
+      </c>
+      <c r="Z4">
+        <v>0.7332064978779453</v>
+      </c>
+      <c r="AA4">
+        <v>0.06783571324036713</v>
+      </c>
+      <c r="AB4">
+        <v>0.06550827272171766</v>
+      </c>
+      <c r="AC4">
+        <v>0.002327440518649471</v>
+      </c>
+      <c r="AD4">
+        <v>517.2</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>517.2</v>
+      </c>
+      <c r="AG4">
+        <v>374.4</v>
+      </c>
+      <c r="AH4">
+        <v>0.2686613682406109</v>
+      </c>
+      <c r="AI4">
+        <v>0.5931192660550459</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2100656455142232</v>
+      </c>
+      <c r="AK4">
+        <v>0.5134393856280856</v>
+      </c>
+      <c r="AL4">
+        <v>19.5</v>
+      </c>
+      <c r="AM4">
+        <v>9.4</v>
+      </c>
+      <c r="AN4">
+        <v>6.751958224543082</v>
+      </c>
+      <c r="AO4">
+        <v>3.430769230769231</v>
+      </c>
+      <c r="AP4">
+        <v>4.887728459530027</v>
+      </c>
+      <c r="AQ4">
+        <v>7.117021276595745</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Confinvest F.L. S.p.A. (BIT:CFV)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.158</v>
+      </c>
+      <c r="E5">
+        <v>0.0333</v>
+      </c>
+      <c r="G5">
+        <v>0.006009975062344139</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.454</v>
+      </c>
+      <c r="L5">
+        <v>0.0113216957605985</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.453</v>
+      </c>
+      <c r="V5">
+        <v>0.03566929133858268</v>
+      </c>
+      <c r="W5">
+        <v>0.06837349397590362</v>
+      </c>
+      <c r="X5">
+        <v>0.0642391179092109</v>
+      </c>
+      <c r="Y5">
+        <v>0.004134376066692716</v>
+      </c>
+      <c r="Z5">
+        <v>7.413569975965983</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06382579734589924</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06382579734589924</v>
+      </c>
+      <c r="AD5">
+        <v>0.999</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0.999</v>
+      </c>
+      <c r="AG5">
+        <v>0.546</v>
+      </c>
+      <c r="AH5">
+        <v>0.07292503102416235</v>
+      </c>
+      <c r="AI5">
+        <v>0.1259931895573212</v>
+      </c>
+      <c r="AJ5">
+        <v>0.04121999094066134</v>
+      </c>
+      <c r="AK5">
+        <v>0.07303370786516855</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Conafi S.p.A. (BIT:CNF)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.254</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>-1.55</v>
+      </c>
+      <c r="L6">
+        <v>-0.2545155993431856</v>
+      </c>
+      <c r="M6">
+        <v>0.486</v>
+      </c>
+      <c r="N6">
+        <v>0.04673076923076923</v>
+      </c>
+      <c r="O6">
+        <v>-0.3135483870967742</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0.486</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>4.46</v>
+      </c>
+      <c r="V6">
+        <v>0.4288461538461538</v>
+      </c>
+      <c r="W6">
+        <v>-0.09935897435897437</v>
+      </c>
+      <c r="X6">
+        <v>0.06458485561172997</v>
+      </c>
+      <c r="Y6">
+        <v>-0.1639438299707043</v>
+      </c>
+      <c r="Z6">
+        <v>0.5794481446241675</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06401438586485786</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06401438586485786</v>
+      </c>
+      <c r="AD6">
+        <v>1.09</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>1.09</v>
+      </c>
+      <c r="AG6">
+        <v>-3.37</v>
+      </c>
+      <c r="AH6">
+        <v>0.09486510008703221</v>
+      </c>
+      <c r="AI6">
+        <v>0.05564063297600817</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.4793741109530583</v>
+      </c>
+      <c r="AK6">
+        <v>-0.2227362855254462</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-0.128</v>
+      </c>
+      <c r="AQ6">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BFF Bank S.p.A. (BIT:BFF)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.194</v>
+      </c>
+      <c r="E7">
+        <v>0.212</v>
+      </c>
+      <c r="F7">
+        <v>0.121</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>275</v>
+      </c>
+      <c r="L7">
+        <v>0.5026503381465911</v>
+      </c>
+      <c r="M7">
+        <v>113.2434</v>
+      </c>
+      <c r="N7">
+        <v>0.06332106911205547</v>
+      </c>
+      <c r="O7">
+        <v>0.4117941818181818</v>
+      </c>
+      <c r="P7">
+        <v>113.2434</v>
+      </c>
+      <c r="Q7">
+        <v>0.06332106911205547</v>
+      </c>
+      <c r="R7">
+        <v>0.4117941818181818</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>186.9</v>
+      </c>
+      <c r="V7">
+        <v>0.1045068217401029</v>
+      </c>
+      <c r="W7">
+        <v>0.3716718475469658</v>
+      </c>
+      <c r="X7">
+        <v>0.06573062510156116</v>
+      </c>
+      <c r="Y7">
+        <v>0.3059412224454047</v>
+      </c>
+      <c r="Z7">
+        <v>2.085064217386333</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06458019881002439</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06458019881002439</v>
+      </c>
+      <c r="AD7">
+        <v>342.4</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>342.4</v>
+      </c>
+      <c r="AG7">
+        <v>155.5</v>
+      </c>
+      <c r="AH7">
+        <v>0.1606908203491646</v>
+      </c>
+      <c r="AI7">
+        <v>0.2678557459125401</v>
+      </c>
+      <c r="AJ7">
+        <v>0.07999382684294458</v>
+      </c>
+      <c r="AK7">
+        <v>0.1424775517683709</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mittel S.p.A. (BIT:MIT)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>9.41</v>
+      </c>
+      <c r="L8">
+        <v>0.0531638418079096</v>
+      </c>
+      <c r="M8">
+        <v>10.7</v>
+      </c>
+      <c r="N8">
+        <v>0.07239512855209741</v>
+      </c>
+      <c r="O8">
+        <v>1.137088204038257</v>
+      </c>
+      <c r="P8">
+        <v>10.7</v>
+      </c>
+      <c r="Q8">
+        <v>0.07239512855209741</v>
+      </c>
+      <c r="R8">
+        <v>1.137088204038257</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>83.8</v>
+      </c>
+      <c r="V8">
+        <v>0.5669824086603518</v>
+      </c>
+      <c r="W8">
+        <v>0.03388548793662226</v>
+      </c>
+      <c r="X8">
+        <v>0.0678065077610511</v>
+      </c>
+      <c r="Y8">
+        <v>-0.03392101982442884</v>
+      </c>
+      <c r="Z8">
+        <v>1.126670910248249</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06542010784267852</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06542010784267852</v>
+      </c>
+      <c r="AD8">
+        <v>51.5</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>51.5</v>
+      </c>
+      <c r="AG8">
+        <v>-32.3</v>
+      </c>
+      <c r="AH8">
+        <v>0.2584044154540893</v>
+      </c>
+      <c r="AI8">
+        <v>0.1473112128146453</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.2796536796536796</v>
+      </c>
+      <c r="AK8">
+        <v>-0.1215199398043642</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-5.11</v>
+      </c>
+      <c r="AQ8">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A. (BIT:GF)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>0.2</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>20.1</v>
+      </c>
+      <c r="L9">
+        <v>0.3964497041420119</v>
+      </c>
+      <c r="M9">
+        <v>8.31</v>
+      </c>
+      <c r="N9">
+        <v>0.05021148036253777</v>
+      </c>
+      <c r="O9">
+        <v>0.4134328358208955</v>
+      </c>
+      <c r="P9">
+        <v>8.31</v>
+      </c>
+      <c r="Q9">
+        <v>0.05021148036253777</v>
+      </c>
+      <c r="R9">
+        <v>0.4134328358208955</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>132.6</v>
+      </c>
+      <c r="V9">
+        <v>0.8012084592145015</v>
+      </c>
+      <c r="W9">
+        <v>0.3059360730593607</v>
+      </c>
+      <c r="X9">
+        <v>0.08762394935347252</v>
+      </c>
+      <c r="Y9">
+        <v>0.2183121237058882</v>
+      </c>
+      <c r="Z9">
+        <v>0.197506817296455</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06704980892815343</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06704980892815343</v>
+      </c>
+      <c r="AD9">
+        <v>305.7</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>305.7</v>
+      </c>
+      <c r="AG9">
+        <v>173.1</v>
+      </c>
+      <c r="AH9">
+        <v>0.6487691001697793</v>
+      </c>
+      <c r="AI9">
+        <v>0.7907397827211587</v>
+      </c>
+      <c r="AJ9">
+        <v>0.5112226816302421</v>
+      </c>
+      <c r="AK9">
+        <v>0.681496062992126</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Banca IFIS S.p.A. (BIT:IF)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="E10">
+        <v>0.027</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>180.6</v>
+      </c>
+      <c r="L10">
+        <v>0.2446822923723073</v>
+      </c>
+      <c r="M10">
+        <v>193.568</v>
+      </c>
+      <c r="N10">
+        <v>0.1679257395679709</v>
+      </c>
+      <c r="O10">
+        <v>1.071805094130676</v>
+      </c>
+      <c r="P10">
+        <v>193.568</v>
+      </c>
+      <c r="Q10">
+        <v>0.1679257395679709</v>
+      </c>
+      <c r="R10">
+        <v>1.071805094130676</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>763.1</v>
+      </c>
+      <c r="V10">
+        <v>0.6620109308579856</v>
+      </c>
+      <c r="W10">
+        <v>0.1008882185352774</v>
+      </c>
+      <c r="X10">
+        <v>0.1233922736909157</v>
+      </c>
+      <c r="Y10">
+        <v>-0.02250405515563837</v>
+      </c>
+      <c r="Z10">
+        <v>0.1045956325194496</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.0680655047446752</v>
+      </c>
+      <c r="AC10">
+        <v>-0.0680655047446752</v>
+      </c>
+      <c r="AD10">
+        <v>5247.2</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>5247.2</v>
+      </c>
+      <c r="AG10">
+        <v>4484.099999999999</v>
+      </c>
+      <c r="AH10">
+        <v>0.819887810747043</v>
+      </c>
+      <c r="AI10">
+        <v>0.725462815744722</v>
+      </c>
+      <c r="AJ10">
+        <v>0.7955045415838774</v>
+      </c>
+      <c r="AK10">
+        <v>0.6930817026801447</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Banca Mediolanum S.p.A. (BIT:BMED)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D11">
         <v>0.15</v>
       </c>
-      <c r="E4">
+      <c r="E11">
         <v>0.281</v>
       </c>
-      <c r="F4">
+      <c r="F11">
         <v>0.0563</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>1030.6</v>
       </c>
-      <c r="L4">
+      <c r="L11">
         <v>0.4419193002015351</v>
       </c>
-      <c r="M4">
+      <c r="M11">
         <v>649.6494</v>
       </c>
-      <c r="N4">
+      <c r="N11">
         <v>0.07406281636189521</v>
       </c>
-      <c r="O4">
+      <c r="O11">
         <v>0.6303603725984864</v>
       </c>
-      <c r="P4">
+      <c r="P11">
         <v>649.6494</v>
       </c>
-      <c r="Q4">
+      <c r="Q11">
         <v>0.07406281636189521</v>
       </c>
-      <c r="R4">
+      <c r="R11">
         <v>0.6303603725984864</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
         <v>202.4</v>
       </c>
-      <c r="V4">
+      <c r="V11">
         <v>0.02307446759998176</v>
       </c>
-      <c r="W4">
+      <c r="W11">
         <v>0.2830852057353183</v>
       </c>
-      <c r="X4">
-        <v>0.07683893084399333</v>
-      </c>
-      <c r="Y4">
-        <v>0.206246274891325</v>
-      </c>
-      <c r="Z4">
+      <c r="X11">
+        <v>0.07683311732773149</v>
+      </c>
+      <c r="Y11">
+        <v>0.2062520884075868</v>
+      </c>
+      <c r="Z11">
         <v>0.1738712274841942</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.06852993109035777</v>
-      </c>
-      <c r="AC4">
-        <v>-0.06852993109035777</v>
-      </c>
-      <c r="AD4">
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.06852706880860547</v>
+      </c>
+      <c r="AC11">
+        <v>-0.06852706880860547</v>
+      </c>
+      <c r="AD11">
         <v>9044.200000000001</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
         <v>9044.200000000001</v>
       </c>
-      <c r="AG4">
+      <c r="AG11">
         <v>8841.800000000001</v>
       </c>
-      <c r="AH4">
+      <c r="AH11">
         <v>0.5076505124664623</v>
       </c>
-      <c r="AI4">
+      <c r="AI11">
         <v>0.6764041582529355</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ11">
         <v>0.5019928009356512</v>
       </c>
-      <c r="AK4">
+      <c r="AK11">
         <v>0.6714305241255714</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>illimity Bank S.p.A. (BIT:ILTY)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.65</v>
+      </c>
+      <c r="F12">
+        <v>0.19</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>67.3</v>
+      </c>
+      <c r="L12">
+        <v>0.2016177351707609</v>
+      </c>
+      <c r="M12">
+        <v>23.074</v>
+      </c>
+      <c r="N12">
+        <v>0.0816489738145789</v>
+      </c>
+      <c r="O12">
+        <v>0.3428528974739971</v>
+      </c>
+      <c r="P12">
+        <v>23.074</v>
+      </c>
+      <c r="Q12">
+        <v>0.0816489738145789</v>
+      </c>
+      <c r="R12">
+        <v>0.3428528974739971</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>410.7</v>
+      </c>
+      <c r="V12">
+        <v>1.453290870488323</v>
+      </c>
+      <c r="W12">
+        <v>0.06931712843753218</v>
+      </c>
+      <c r="X12">
+        <v>0.1750347570169343</v>
+      </c>
+      <c r="Y12">
+        <v>-0.1057176285794021</v>
+      </c>
+      <c r="Z12">
+        <v>0.1368818174362339</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.07088571781027711</v>
+      </c>
+      <c r="AC12">
+        <v>-0.07088571781027711</v>
+      </c>
+      <c r="AD12">
+        <v>2390.1</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>2390.1</v>
+      </c>
+      <c r="AG12">
+        <v>1979.4</v>
+      </c>
+      <c r="AH12">
+        <v>0.8942642271859917</v>
+      </c>
+      <c r="AI12">
+        <v>0.6868498189551123</v>
+      </c>
+      <c r="AJ12">
+        <v>0.8750663129973474</v>
+      </c>
+      <c r="AK12">
+        <v>0.644944772083021</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
         <v>0</v>
       </c>
     </row>
